--- a/benchmarks/COMPARISON/benchmark_summary.xlsx
+++ b/benchmarks/COMPARISON/benchmark_summary.xlsx
@@ -474,22 +474,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.60591205229004</v>
+        <v>16.4892530438246</v>
       </c>
       <c r="C2" t="n">
-        <v>10.65009574298181</v>
+        <v>10.06491306090173</v>
       </c>
       <c r="D2" t="n">
-        <v>59.90590490834383</v>
+        <v>57.3115958212609</v>
       </c>
       <c r="E2" t="n">
-        <v>31.66386642415203</v>
+        <v>30.72766489389882</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7843422461634135</v>
+        <v>0.8009632562995861</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04476810158856316</v>
+        <v>0.04786967801821013</v>
       </c>
     </row>
     <row r="3">
@@ -499,22 +499,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.75088983334027</v>
+        <v>16.62937647342978</v>
       </c>
       <c r="C3" t="n">
-        <v>10.71251155402743</v>
+        <v>10.10416996100279</v>
       </c>
       <c r="D3" t="n">
-        <v>60.24203385982976</v>
+        <v>57.52866129715927</v>
       </c>
       <c r="E3" t="n">
-        <v>32.07196566898905</v>
+        <v>30.72560217608627</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7820199491746609</v>
+        <v>0.7998704904395185</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04800664526757337</v>
+        <v>0.04674810720588136</v>
       </c>
     </row>
     <row r="4">
@@ -524,22 +524,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.12218084335327</v>
+        <v>17.06602458953857</v>
       </c>
       <c r="C4" t="n">
-        <v>11.65970454549263</v>
+        <v>10.86931679545006</v>
       </c>
       <c r="D4" t="n">
-        <v>63.43365743863454</v>
+        <v>61.29638101296401</v>
       </c>
       <c r="E4" t="n">
-        <v>36.29720370790132</v>
+        <v>34.66986417189428</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7675316214561463</v>
+        <v>0.7784385561943055</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03608502617426586</v>
+        <v>0.04463824332293643</v>
       </c>
     </row>
     <row r="5">
@@ -549,22 +549,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.02995998328536</v>
+        <v>20.39980773959659</v>
       </c>
       <c r="C5" t="n">
-        <v>14.85178730294646</v>
+        <v>14.51449821218379</v>
       </c>
       <c r="D5" t="n">
-        <v>79.80343654669635</v>
+        <v>79.21396983754188</v>
       </c>
       <c r="E5" t="n">
-        <v>50.72920845770767</v>
+        <v>51.69124888705274</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6446758601569572</v>
+        <v>0.6535329427274249</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0765549650330208</v>
+        <v>0.07981428359296688</v>
       </c>
     </row>
   </sheetData>
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.60591205229004</v>
+        <v>16.4892530438246</v>
       </c>
       <c r="C2" t="n">
-        <v>10.65009574298181</v>
+        <v>10.06491306090173</v>
       </c>
       <c r="D2" t="n">
-        <v>59.90590490834383</v>
+        <v>57.3115958212609</v>
       </c>
       <c r="E2" t="n">
-        <v>31.66386642415203</v>
+        <v>30.72766489389882</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7843422461634135</v>
+        <v>0.8009632562995861</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04476810158856316</v>
+        <v>0.04786967801821013</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -658,22 +658,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.75088983334027</v>
+        <v>16.62937647342978</v>
       </c>
       <c r="C3" t="n">
-        <v>10.71251155402743</v>
+        <v>10.10416996100279</v>
       </c>
       <c r="D3" t="n">
-        <v>60.24203385982976</v>
+        <v>57.52866129715927</v>
       </c>
       <c r="E3" t="n">
-        <v>32.07196566898905</v>
+        <v>30.72560217608627</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7820199491746609</v>
+        <v>0.7998704904395185</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04800664526757337</v>
+        <v>0.04674810720588136</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.12218084335327</v>
+        <v>17.06602458953857</v>
       </c>
       <c r="C4" t="n">
-        <v>11.65970454549263</v>
+        <v>10.86931679545006</v>
       </c>
       <c r="D4" t="n">
-        <v>63.43365743863454</v>
+        <v>61.29638101296401</v>
       </c>
       <c r="E4" t="n">
-        <v>36.29720370790132</v>
+        <v>34.66986417189428</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7675316214561463</v>
+        <v>0.7784385561943055</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03608502617426586</v>
+        <v>0.04463824332293643</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.02995998328536</v>
+        <v>20.39980773959659</v>
       </c>
       <c r="C5" t="n">
-        <v>14.85178730294646</v>
+        <v>14.51449821218379</v>
       </c>
       <c r="D5" t="n">
-        <v>79.80343654669635</v>
+        <v>79.21396983754188</v>
       </c>
       <c r="E5" t="n">
-        <v>50.72920845770767</v>
+        <v>51.69124888705274</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6446758601569572</v>
+        <v>0.6535329427274249</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0765549650330208</v>
+        <v>0.07981428359296688</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7843422461634135</v>
+        <v>0.8009632562995861</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.202593456920228</v>
+        <v>-0.1859724467840554</v>
       </c>
     </row>
   </sheetData>
